--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run4/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,766 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8066,0.1286,0.0112,0.0247</t>
-  </si>
-  <si>
-    <t>0.0484,0.0008,0.0001,0.9884</t>
-  </si>
-  <si>
-    <t>0.6057,0.2154,0.0084,0.1572</t>
-  </si>
-  <si>
-    <t>0.0941,0.0168,0.0006,0.9563</t>
-  </si>
-  <si>
-    <t>0.9976,0.0018,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9898,0.0099,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9957,0.0034,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0010,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9934,0.0093,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.7784,0.1350,0.0801,0.0237</t>
-  </si>
-  <si>
-    <t>0.5719,0.0392,0.5096,0.0051</t>
-  </si>
-  <si>
-    <t>0.5364,0.0142,0.6749,0.0009</t>
-  </si>
-  <si>
-    <t>0.1646,0.0919,0.7397,0.0045</t>
-  </si>
-  <si>
-    <t>0.6102,0.0691,0.3750,0.0349</t>
-  </si>
-  <si>
-    <t>0.0039,0.9917,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.0064,0.9875,0.0103,0.0004</t>
-  </si>
-  <si>
-    <t>0.3038,0.7894,0.0108,0.0037</t>
-  </si>
-  <si>
-    <t>0.0067,0.9893,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.9985,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.6244,0.0264,0.3568,0.0381</t>
-  </si>
-  <si>
-    <t>0.5792,0.0163,0.5185,0.0092</t>
-  </si>
-  <si>
-    <t>0.0279,0.0055,0.9636,0.0075</t>
-  </si>
-  <si>
-    <t>0.5855,0.0151,0.5184,0.0079</t>
-  </si>
-  <si>
-    <t>0.1971,0.1198,0.6311,0.1147</t>
-  </si>
-  <si>
-    <t>0.0913,0.1078,0.7910,0.0183</t>
-  </si>
-  <si>
-    <t>0.0122,0.0009,0.9878,0.0013</t>
-  </si>
-  <si>
-    <t>0.3661,0.6733,0.0384,0.0048</t>
-  </si>
-  <si>
-    <t>0.9086,0.0554,0.0323,0.0038</t>
-  </si>
-  <si>
-    <t>0.0005,0.0065,0.9940,0.0147</t>
-  </si>
-  <si>
-    <t>0.0977,0.7130,0.2227,0.0031</t>
-  </si>
-  <si>
-    <t>0.9502,0.0310,0.0087,0.0044</t>
-  </si>
-  <si>
-    <t>0.9097,0.0572,0.0377,0.0059</t>
-  </si>
-  <si>
-    <t>0.7876,0.3595,0.0036,0.0011</t>
-  </si>
-  <si>
-    <t>0.0736,0.8860,0.1834,0.0037</t>
-  </si>
-  <si>
-    <t>0.0234,0.5016,0.7228,0.0510</t>
-  </si>
-  <si>
-    <t>0.0247,0.0337,0.9303,0.0416</t>
-  </si>
-  <si>
-    <t>0.2125,0.0244,0.8277,0.0097</t>
-  </si>
-  <si>
-    <t>0.0456,0.0038,0.9322,0.0290</t>
-  </si>
-  <si>
-    <t>0.0500,0.3732,0.8163,0.0161</t>
-  </si>
-  <si>
-    <t>0.0082,0.9674,0.0354,0.0007</t>
-  </si>
-  <si>
-    <t>0.0689,0.0779,0.8870,0.0095</t>
-  </si>
-  <si>
-    <t>0.0428,0.4173,0.0010,0.7997</t>
-  </si>
-  <si>
-    <t>0.0322,0.9693,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.0019,0.9728,0.3165,0.0002</t>
-  </si>
-  <si>
-    <t>0.0038,0.9760,0.2040,0.0019</t>
-  </si>
-  <si>
-    <t>0.0147,0.0130,0.9552,0.0301</t>
-  </si>
-  <si>
-    <t>0.0163,0.0088,0.9849,0.0002</t>
-  </si>
-  <si>
-    <t>0.0763,0.0065,0.9293,0.0100</t>
-  </si>
-  <si>
-    <t>0.0198,0.0013,0.9857,0.0006</t>
-  </si>
-  <si>
-    <t>0.0350,0.0033,0.9641,0.0049</t>
-  </si>
-  <si>
-    <t>0.0129,0.0882,0.9694,0.0008</t>
-  </si>
-  <si>
-    <t>0.9547,0.0516,0.0035,0.0022</t>
-  </si>
-  <si>
-    <t>0.9627,0.0311,0.0032,0.0026</t>
-  </si>
-  <si>
-    <t>0.9932,0.0041,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.0066,0.0848,0.9773,0.0052</t>
-  </si>
-  <si>
-    <t>0.9958,0.0018,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9957,0.0023,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9898,0.0149,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0114,0.8166,0.7750,0.0069</t>
-  </si>
-  <si>
-    <t>0.0025,0.1119,0.9901,0.0004</t>
-  </si>
-  <si>
-    <t>0.0042,0.0030,0.9781,0.0361</t>
-  </si>
-  <si>
-    <t>0.0027,0.8865,0.8502,0.0003</t>
-  </si>
-  <si>
-    <t>0.0064,0.0849,0.9784,0.0004</t>
-  </si>
-  <si>
-    <t>0.0679,0.8487,0.1501,0.0035</t>
-  </si>
-  <si>
-    <t>0.0126,0.9808,0.0039,0.0008</t>
-  </si>
-  <si>
-    <t>0.8894,0.0723,0.0334,0.0022</t>
-  </si>
-  <si>
-    <t>0.8510,0.0963,0.0749,0.0026</t>
-  </si>
-  <si>
-    <t>0.0016,0.0133,0.9936,0.0034</t>
-  </si>
-  <si>
-    <t>0.0070,0.6205,0.9079,0.0005</t>
-  </si>
-  <si>
-    <t>0.0026,0.8610,0.9317,0.0004</t>
-  </si>
-  <si>
-    <t>0.0012,0.9641,0.3241,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.9253,0.9048,0.0004</t>
-  </si>
-  <si>
-    <t>0.0061,0.0009,0.0161,0.9896</t>
-  </si>
-  <si>
-    <t>0.0202,0.0052,0.0005,0.9923</t>
-  </si>
-  <si>
-    <t>0.0024,0.0102,0.0001,0.9980</t>
-  </si>
-  <si>
-    <t>0.0198,0.0243,0.0037,0.9844</t>
-  </si>
-  <si>
-    <t>0.0148,0.0009,0.0012,0.9929</t>
-  </si>
-  <si>
-    <t>0.0236,0.0041,0.0019,0.9884</t>
-  </si>
-  <si>
-    <t>0.0030,0.9595,0.4775,0.0009</t>
-  </si>
-  <si>
-    <t>0.0016,0.7369,0.9537,0.0001</t>
-  </si>
-  <si>
-    <t>0.0451,0.1904,0.8545,0.0061</t>
-  </si>
-  <si>
-    <t>0.0285,0.2547,0.8866,0.0087</t>
-  </si>
-  <si>
-    <t>0.0015,0.9839,0.0987,0.0003</t>
-  </si>
-  <si>
-    <t>0.0038,0.7239,0.7829,0.0001</t>
-  </si>
-  <si>
-    <t>0.9961,0.0045,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9657,0.0744,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9864,0.0130,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9951,0.0030,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9963,0.0013,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9927,0.0098,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9836,0.0128,0.0032,0.0006</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0019,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0017,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0007,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0922,0.0043,0.9180,0.0100</t>
-  </si>
-  <si>
-    <t>0.2706,0.0064,0.8379,0.0011</t>
-  </si>
-  <si>
-    <t>0.7210,0.0195,0.2980,0.0265</t>
-  </si>
-  <si>
-    <t>0.2566,0.0040,0.8236,0.0065</t>
-  </si>
-  <si>
-    <t>0.0387,0.9413,0.0052,0.0093</t>
-  </si>
-  <si>
-    <t>0.0334,0.9539,0.0088,0.0030</t>
-  </si>
-  <si>
-    <t>0.0252,0.9639,0.0054,0.0017</t>
-  </si>
-  <si>
-    <t>0.3201,0.7662,0.0012,0.0030</t>
-  </si>
-  <si>
-    <t>0.0137,0.9723,0.0017,0.0045</t>
-  </si>
-  <si>
-    <t>0.0025,0.9950,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.7541,0.3801,0.0023,0.0018</t>
-  </si>
-  <si>
-    <t>0.8051,0.0322,0.1116,0.0404</t>
-  </si>
-  <si>
-    <t>0.2837,0.0563,0.7353,0.0072</t>
-  </si>
-  <si>
-    <t>0.8255,0.0540,0.1193,0.0069</t>
-  </si>
-  <si>
-    <t>0.3290,0.1454,0.5767,0.0373</t>
-  </si>
-  <si>
-    <t>0.1370,0.0454,0.0455,0.8812</t>
-  </si>
-  <si>
-    <t>0.0073,0.9753,0.0908,0.0012</t>
-  </si>
-  <si>
-    <t>0.0013,0.9945,0.0136,0.0007</t>
-  </si>
-  <si>
-    <t>0.0076,0.9331,0.0372,0.3613</t>
-  </si>
-  <si>
-    <t>0.0004,0.9360,0.9682,0.0001</t>
-  </si>
-  <si>
-    <t>0.0300,0.9716,0.0292,0.0003</t>
-  </si>
-  <si>
-    <t>0.5343,0.5708,0.0243,0.0006</t>
-  </si>
-  <si>
-    <t>0.5952,0.5343,0.0060,0.0019</t>
-  </si>
-  <si>
-    <t>0.9919,0.0055,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9907,0.0040,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.9896,0.0014,0.0006,0.0035</t>
-  </si>
-  <si>
-    <t>0.9836,0.0028,0.0042,0.0034</t>
-  </si>
-  <si>
-    <t>0.9965,0.0007,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9934,0.0053,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9923,0.0006,0.0002,0.0032</t>
-  </si>
-  <si>
-    <t>0.9838,0.0113,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.0097,0.3256,0.9566,0.0005</t>
-  </si>
-  <si>
-    <t>0.0023,0.6042,0.9680,0.0001</t>
-  </si>
-  <si>
-    <t>0.0093,0.4968,0.8889,0.0009</t>
-  </si>
-  <si>
-    <t>0.0182,0.0301,0.9691,0.0011</t>
-  </si>
-  <si>
-    <t>0.7767,0.0806,0.0294,0.1093</t>
-  </si>
-  <si>
-    <t>0.9257,0.0189,0.0357,0.0046</t>
-  </si>
-  <si>
-    <t>0.7205,0.0047,0.4222,0.0047</t>
-  </si>
-  <si>
-    <t>0.6443,0.2713,0.1177,0.0143</t>
-  </si>
-  <si>
-    <t>0.0345,0.0016,0.0022,0.9842</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.0006,0.9992</t>
-  </si>
-  <si>
-    <t>0.0026,0.0127,0.0003,0.9980</t>
-  </si>
-  <si>
-    <t>0.0580,0.0075,0.0041,0.9707</t>
-  </si>
-  <si>
-    <t>0.0018,0.7398,0.7809,0.0052</t>
-  </si>
-  <si>
-    <t>0.9881,0.0048,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.0723,0.9152,0.0054,0.0103</t>
-  </si>
-  <si>
-    <t>0.9931,0.0026,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.7032,0.3933,0.0220,0.0054</t>
-  </si>
-  <si>
-    <t>0.9823,0.0137,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.8725,0.0128,0.0208,0.0981</t>
-  </si>
-  <si>
-    <t>0.9803,0.0032,0.0007,0.0072</t>
-  </si>
-  <si>
-    <t>0.0002,0.0129,0.9873,0.0477</t>
-  </si>
-  <si>
-    <t>0.8888,0.0003,0.0005,0.2200</t>
-  </si>
-  <si>
-    <t>0.9709,0.0037,0.0011,0.0165</t>
-  </si>
-  <si>
-    <t>0.8143,0.1928,0.0030,0.0119</t>
-  </si>
-  <si>
-    <t>0.9769,0.0126,0.0030,0.0007</t>
-  </si>
-  <si>
-    <t>0.8564,0.1676,0.0168,0.0016</t>
-  </si>
-  <si>
-    <t>0.0442,0.9360,0.0078,0.0138</t>
-  </si>
-  <si>
-    <t>0.8990,0.0805,0.0311,0.0016</t>
-  </si>
-  <si>
-    <t>0.9688,0.0154,0.0111,0.0013</t>
-  </si>
-  <si>
-    <t>0.9946,0.0006,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9954,0.0020,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9974,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0001,0.0000,0.0011</t>
-  </si>
-  <si>
-    <t>0.9887,0.0031,0.0010,0.0021</t>
-  </si>
-  <si>
-    <t>0.9700,0.0279,0.0025,0.0009</t>
-  </si>
-  <si>
-    <t>0.9965,0.0004,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9969,0.0003,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9312,0.0861,0.0020,0.0022</t>
-  </si>
-  <si>
-    <t>0.8438,0.2266,0.0073,0.0001</t>
-  </si>
-  <si>
-    <t>0.8808,0.2205,0.0019,0.0008</t>
-  </si>
-  <si>
-    <t>0.3306,0.1845,0.6539,0.0047</t>
-  </si>
-  <si>
-    <t>0.9402,0.0875,0.0041,0.0009</t>
-  </si>
-  <si>
-    <t>0.9307,0.0850,0.0057,0.0020</t>
-  </si>
-  <si>
-    <t>0.9646,0.0349,0.0046,0.0013</t>
-  </si>
-  <si>
-    <t>0.9698,0.0283,0.0021,0.0017</t>
-  </si>
-  <si>
-    <t>0.0002,0.0280,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.9452,0.0675,0.0032,0.0033</t>
-  </si>
-  <si>
-    <t>0.0063,0.0021,0.9913,0.0009</t>
-  </si>
-  <si>
-    <t>0.0261,0.0641,0.9585,0.0031</t>
-  </si>
-  <si>
-    <t>0.0380,0.0050,0.9721,0.0007</t>
-  </si>
-  <si>
-    <t>0.0264,0.0836,0.9498,0.0012</t>
-  </si>
-  <si>
-    <t>0.0199,0.0367,0.9615,0.0004</t>
-  </si>
-  <si>
-    <t>0.0187,0.0079,0.9732,0.0017</t>
-  </si>
-  <si>
-    <t>0.0286,0.0113,0.9615,0.0036</t>
-  </si>
-  <si>
-    <t>0.3006,0.0830,0.6672,0.0214</t>
-  </si>
-  <si>
-    <t>0.3563,0.0517,0.6769,0.0106</t>
-  </si>
-  <si>
-    <t>0.3787,0.5755,0.0801,0.0187</t>
-  </si>
-  <si>
-    <t>0.2040,0.4126,0.4319,0.0030</t>
-  </si>
-  <si>
-    <t>0.0405,0.6505,0.3668,0.0012</t>
-  </si>
-  <si>
-    <t>0.7104,0.0520,0.2946,0.0037</t>
-  </si>
-  <si>
-    <t>0.5229,0.0206,0.5126,0.0257</t>
-  </si>
-  <si>
-    <t>0.3664,0.1805,0.4866,0.0078</t>
-  </si>
-  <si>
-    <t>0.8837,0.2029,0.0043,0.0003</t>
-  </si>
-  <si>
-    <t>0.4884,0.6814,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9530,0.0984,0.0025,0.0004</t>
-  </si>
-  <si>
-    <t>0.9734,0.0327,0.0032,0.0005</t>
-  </si>
-  <si>
-    <t>0.9768,0.0303,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.7141,0.0404,0.3552,0.0101</t>
-  </si>
-  <si>
-    <t>0.8972,0.0072,0.1141,0.0034</t>
-  </si>
-  <si>
-    <t>0.8988,0.0064,0.0179,0.0446</t>
-  </si>
-  <si>
-    <t>0.5762,0.0243,0.5102,0.0122</t>
-  </si>
-  <si>
-    <t>0.8986,0.0143,0.0404,0.0204</t>
-  </si>
-  <si>
-    <t>0.0022,0.0040,0.9631,0.2376</t>
-  </si>
-  <si>
-    <t>0.0539,0.0167,0.9292,0.0146</t>
-  </si>
-  <si>
-    <t>0.0777,0.0675,0.8925,0.0102</t>
-  </si>
-  <si>
-    <t>0.0927,0.0145,0.9083,0.0132</t>
-  </si>
-  <si>
-    <t>0.0313,0.7457,0.5491,0.0056</t>
-  </si>
-  <si>
-    <t>0.9947,0.0032,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9977,0.0010,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9935,0.0036,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9932,0.0043,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9936,0.0026,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9966,0.0030,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9943,0.0013,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9979,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.3929,0.0189,0.7417,0.0040</t>
-  </si>
-  <si>
-    <t>0.0441,0.9234,0.0880,0.0026</t>
-  </si>
-  <si>
-    <t>0.8543,0.0863,0.0567,0.0180</t>
-  </si>
-  <si>
-    <t>0.0275,0.0148,0.9665,0.0020</t>
-  </si>
-  <si>
-    <t>0.0028,0.0085,0.9818,0.0091</t>
-  </si>
-  <si>
-    <t>0.1013,0.1138,0.7835,0.0021</t>
-  </si>
-  <si>
-    <t>0.0091,0.0071,0.9863,0.0022</t>
-  </si>
-  <si>
-    <t>0.0295,0.0085,0.9615,0.0046</t>
-  </si>
-  <si>
-    <t>0.0150,0.0037,0.9879,0.0004</t>
-  </si>
-  <si>
-    <t>0.0725,0.0154,0.9481,0.0015</t>
-  </si>
-  <si>
-    <t>0.3594,0.0555,0.6835,0.0095</t>
-  </si>
-  <si>
-    <t>0.8602,0.0041,0.1854,0.0034</t>
-  </si>
-  <si>
-    <t>0.7444,0.0021,0.3672,0.0061</t>
-  </si>
-  <si>
-    <t>0.8925,0.0299,0.0608,0.0036</t>
-  </si>
-  <si>
-    <t>0.9936,0.0027,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9934,0.0149,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9905,0.0082,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9962,0.0018,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9902,0.0069,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9972,0.0024,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9924,0.0022,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.0098,0.1502,0.9196,0.0037</t>
-  </si>
-  <si>
-    <t>0.0018,0.0486,0.9915,0.0007</t>
-  </si>
-  <si>
-    <t>0.0238,0.0152,0.9675,0.0033</t>
-  </si>
-  <si>
-    <t>0.0295,0.0119,0.9612,0.0005</t>
-  </si>
-  <si>
-    <t>0.0090,0.0035,0.9866,0.0023</t>
-  </si>
-  <si>
-    <t>0.5156,0.0216,0.4650,0.0680</t>
-  </si>
-  <si>
-    <t>0.1047,0.0200,0.8773,0.0204</t>
-  </si>
-  <si>
-    <t>0.0306,0.0270,0.8875,0.1282</t>
-  </si>
-  <si>
-    <t>0.2008,0.0009,0.0091,0.8781</t>
-  </si>
-  <si>
-    <t>0.0293,0.1627,0.0004,0.9314</t>
-  </si>
-  <si>
-    <t>0.0563,0.0217,0.0002,0.9607</t>
-  </si>
-  <si>
-    <t>0.0073,0.0002,0.0005,0.9967</t>
-  </si>
-  <si>
-    <t>0.0064,0.0001,0.0005,0.9964</t>
-  </si>
-  <si>
-    <t>0.7665,0.0351,0.0144,0.1807</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9164,0.0497,0.0021,0.0096</t>
+  </si>
+  <si>
+    <t>0.0148,0.0007,0.0002,0.9955</t>
+  </si>
+  <si>
+    <t>0.5109,0.0060,0.0105,0.6428</t>
+  </si>
+  <si>
+    <t>0.0424,0.0030,0.0005,0.9874</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9962,0.0022,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0014,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0005,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9945,0.0028,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9915,0.0104,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7012,0.0256,0.3354,0.0161</t>
+  </si>
+  <si>
+    <t>0.3791,0.0303,0.7302,0.0048</t>
+  </si>
+  <si>
+    <t>0.4855,0.0155,0.6591,0.0004</t>
+  </si>
+  <si>
+    <t>0.1972,0.0628,0.7721,0.0032</t>
+  </si>
+  <si>
+    <t>0.8086,0.1577,0.0511,0.0110</t>
+  </si>
+  <si>
+    <t>0.0312,0.9632,0.0144,0.0007</t>
+  </si>
+  <si>
+    <t>0.0320,0.9639,0.0113,0.0016</t>
+  </si>
+  <si>
+    <t>0.4302,0.6599,0.0089,0.0049</t>
+  </si>
+  <si>
+    <t>0.0024,0.9927,0.0029,0.0007</t>
+  </si>
+  <si>
+    <t>0.0027,0.9939,0.0046,0.0001</t>
+  </si>
+  <si>
+    <t>0.2987,0.0061,0.5310,0.1346</t>
+  </si>
+  <si>
+    <t>0.3964,0.0075,0.7746,0.0010</t>
+  </si>
+  <si>
+    <t>0.0237,0.0397,0.9469,0.0067</t>
+  </si>
+  <si>
+    <t>0.3054,0.0330,0.6511,0.0826</t>
+  </si>
+  <si>
+    <t>0.0576,0.0080,0.9514,0.0023</t>
+  </si>
+  <si>
+    <t>0.1096,0.0030,0.8405,0.0625</t>
+  </si>
+  <si>
+    <t>0.0053,0.0004,0.9853,0.0116</t>
+  </si>
+  <si>
+    <t>0.6407,0.5088,0.0093,0.0007</t>
+  </si>
+  <si>
+    <t>0.8463,0.0278,0.1161,0.0172</t>
+  </si>
+  <si>
+    <t>0.0121,0.0156,0.9726,0.0125</t>
+  </si>
+  <si>
+    <t>0.0210,0.9543,0.0306,0.0010</t>
+  </si>
+  <si>
+    <t>0.8840,0.0842,0.0602,0.0053</t>
+  </si>
+  <si>
+    <t>0.8696,0.0955,0.0391,0.0157</t>
+  </si>
+  <si>
+    <t>0.1919,0.8394,0.0089,0.0031</t>
+  </si>
+  <si>
+    <t>0.0195,0.9535,0.2086,0.0007</t>
+  </si>
+  <si>
+    <t>0.0031,0.8767,0.3116,0.0222</t>
+  </si>
+  <si>
+    <t>0.0194,0.0021,0.7889,0.2188</t>
+  </si>
+  <si>
+    <t>0.1200,0.0549,0.7878,0.0779</t>
+  </si>
+  <si>
+    <t>0.0596,0.0033,0.8876,0.0589</t>
+  </si>
+  <si>
+    <t>0.0097,0.1994,0.9706,0.0002</t>
+  </si>
+  <si>
+    <t>0.0283,0.7293,0.4081,0.0064</t>
+  </si>
+  <si>
+    <t>0.0087,0.0064,0.9782,0.0128</t>
+  </si>
+  <si>
+    <t>0.0179,0.3663,0.0013,0.9446</t>
+  </si>
+  <si>
+    <t>0.0255,0.9612,0.0117,0.0059</t>
+  </si>
+  <si>
+    <t>0.0026,0.9782,0.1574,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9925,0.1491,0.0003</t>
+  </si>
+  <si>
+    <t>0.0341,0.1017,0.9101,0.0267</t>
+  </si>
+  <si>
+    <t>0.0039,0.3261,0.9810,0.0003</t>
+  </si>
+  <si>
+    <t>0.2813,0.0128,0.7847,0.0060</t>
+  </si>
+  <si>
+    <t>0.1233,0.0021,0.9401,0.0012</t>
+  </si>
+  <si>
+    <t>0.0150,0.0121,0.9592,0.0250</t>
+  </si>
+  <si>
+    <t>0.0066,0.0927,0.9715,0.0006</t>
+  </si>
+  <si>
+    <t>0.9486,0.0782,0.0026,0.0014</t>
+  </si>
+  <si>
+    <t>0.9559,0.0515,0.0078,0.0011</t>
+  </si>
+  <si>
+    <t>0.9783,0.0350,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.0142,0.0568,0.9812,0.0016</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9923,0.0035,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.0028,0.7724,0.8579,0.0065</t>
+  </si>
+  <si>
+    <t>0.0036,0.2748,0.9757,0.0027</t>
+  </si>
+  <si>
+    <t>0.0026,0.0044,0.9899,0.0059</t>
+  </si>
+  <si>
+    <t>0.0013,0.9135,0.9486,0.0003</t>
+  </si>
+  <si>
+    <t>0.0343,0.0088,0.9731,0.0007</t>
+  </si>
+  <si>
+    <t>0.0812,0.8245,0.0604,0.0003</t>
+  </si>
+  <si>
+    <t>0.0673,0.9478,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9129,0.0293,0.0578,0.0036</t>
+  </si>
+  <si>
+    <t>0.8328,0.0957,0.0908,0.0047</t>
+  </si>
+  <si>
+    <t>0.0087,0.0185,0.9802,0.0081</t>
+  </si>
+  <si>
+    <t>0.0026,0.9126,0.8283,0.0002</t>
+  </si>
+  <si>
+    <t>0.0050,0.7287,0.8896,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.9881,0.1220,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.9665,0.9428,0.0001</t>
+  </si>
+  <si>
+    <t>0.0315,0.0080,0.0127,0.9745</t>
+  </si>
+  <si>
+    <t>0.0066,0.0009,0.0000,0.9976</t>
+  </si>
+  <si>
+    <t>0.0031,0.0133,0.0002,0.9971</t>
+  </si>
+  <si>
+    <t>0.0060,0.0013,0.0031,0.9947</t>
+  </si>
+  <si>
+    <t>0.0025,0.0776,0.0048,0.9929</t>
+  </si>
+  <si>
+    <t>0.0182,0.0280,0.0004,0.9863</t>
+  </si>
+  <si>
+    <t>0.0008,0.9472,0.9488,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.8403,0.9379,0.0004</t>
+  </si>
+  <si>
+    <t>0.1517,0.0681,0.8258,0.0023</t>
+  </si>
+  <si>
+    <t>0.0198,0.3762,0.9235,0.0046</t>
+  </si>
+  <si>
+    <t>0.0018,0.8614,0.8718,0.0001</t>
+  </si>
+  <si>
+    <t>0.0332,0.5406,0.6341,0.0003</t>
+  </si>
+  <si>
+    <t>0.9849,0.0179,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.9861,0.0190,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9630,0.0469,0.0033,0.0011</t>
+  </si>
+  <si>
+    <t>0.9930,0.0039,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9829,0.0247,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9925,0.0055,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9685,0.0447,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0034,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.0028,0.9901,0.0122</t>
+  </si>
+  <si>
+    <t>0.0258,0.0399,0.9562,0.0017</t>
+  </si>
+  <si>
+    <t>0.9394,0.0041,0.0320,0.0035</t>
+  </si>
+  <si>
+    <t>0.5289,0.0116,0.5712,0.0139</t>
+  </si>
+  <si>
+    <t>0.0166,0.9799,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.0119,0.9836,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.0501,0.9374,0.0113,0.0034</t>
+  </si>
+  <si>
+    <t>0.1261,0.8889,0.0061,0.0022</t>
+  </si>
+  <si>
+    <t>0.0134,0.9714,0.0016,0.0075</t>
+  </si>
+  <si>
+    <t>0.0091,0.9861,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.7320,0.4077,0.0032,0.0012</t>
+  </si>
+  <si>
+    <t>0.7847,0.0692,0.1419,0.0305</t>
+  </si>
+  <si>
+    <t>0.3085,0.0080,0.8471,0.0005</t>
+  </si>
+  <si>
+    <t>0.6270,0.0413,0.0331,0.3231</t>
+  </si>
+  <si>
+    <t>0.8492,0.0271,0.1466,0.0054</t>
+  </si>
+  <si>
+    <t>0.2515,0.1153,0.0554,0.7882</t>
+  </si>
+  <si>
+    <t>0.0187,0.9746,0.0099,0.0021</t>
+  </si>
+  <si>
+    <t>0.0055,0.9861,0.0111,0.0014</t>
+  </si>
+  <si>
+    <t>0.0040,0.9732,0.0250,0.0827</t>
+  </si>
+  <si>
+    <t>0.0045,0.9317,0.7386,0.0015</t>
+  </si>
+  <si>
+    <t>0.0438,0.9709,0.0063,0.0002</t>
+  </si>
+  <si>
+    <t>0.7110,0.3314,0.0391,0.0016</t>
+  </si>
+  <si>
+    <t>0.8168,0.2947,0.0047,0.0015</t>
+  </si>
+  <si>
+    <t>0.9931,0.0087,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9898,0.0056,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9870,0.0020,0.0005,0.0049</t>
+  </si>
+  <si>
+    <t>0.9754,0.0072,0.0017,0.0080</t>
+  </si>
+  <si>
+    <t>0.9966,0.0006,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9856,0.0037,0.0051,0.0018</t>
+  </si>
+  <si>
+    <t>0.9931,0.0009,0.0006,0.0022</t>
+  </si>
+  <si>
+    <t>0.9959,0.0006,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.0105,0.1950,0.9569,0.0017</t>
+  </si>
+  <si>
+    <t>0.0102,0.3526,0.9326,0.0001</t>
+  </si>
+  <si>
+    <t>0.0754,0.0632,0.8986,0.0014</t>
+  </si>
+  <si>
+    <t>0.0954,0.0095,0.9370,0.0011</t>
+  </si>
+  <si>
+    <t>0.8984,0.0232,0.0678,0.0108</t>
+  </si>
+  <si>
+    <t>0.8423,0.0137,0.2471,0.0021</t>
+  </si>
+  <si>
+    <t>0.2272,0.0104,0.8569,0.0018</t>
+  </si>
+  <si>
+    <t>0.7687,0.0217,0.2135,0.0194</t>
+  </si>
+  <si>
+    <t>0.0829,0.0039,0.0031,0.9640</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.0002,0.9992</t>
+  </si>
+  <si>
+    <t>0.0015,0.0060,0.0022,0.9974</t>
+  </si>
+  <si>
+    <t>0.0077,0.0037,0.0007,0.9960</t>
+  </si>
+  <si>
+    <t>0.0067,0.9406,0.1966,0.0073</t>
+  </si>
+  <si>
+    <t>0.9878,0.0063,0.0020,0.0008</t>
+  </si>
+  <si>
+    <t>0.0099,0.9760,0.0012,0.0117</t>
+  </si>
+  <si>
+    <t>0.9860,0.0109,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.8900,0.1014,0.0241,0.0037</t>
+  </si>
+  <si>
+    <t>0.9873,0.0024,0.0004,0.0041</t>
+  </si>
+  <si>
+    <t>0.8596,0.0121,0.0084,0.1390</t>
+  </si>
+  <si>
+    <t>0.9864,0.0033,0.0007,0.0035</t>
+  </si>
+  <si>
+    <t>0.0005,0.1181,0.9918,0.0023</t>
+  </si>
+  <si>
+    <t>0.9299,0.0013,0.0036,0.0705</t>
+  </si>
+  <si>
+    <t>0.9608,0.0095,0.0035,0.0143</t>
+  </si>
+  <si>
+    <t>0.5402,0.4903,0.0202,0.0101</t>
+  </si>
+  <si>
+    <t>0.9676,0.0272,0.0032,0.0005</t>
+  </si>
+  <si>
+    <t>0.8539,0.0958,0.0535,0.0055</t>
+  </si>
+  <si>
+    <t>0.0385,0.9217,0.0021,0.0347</t>
+  </si>
+  <si>
+    <t>0.9078,0.0948,0.0177,0.0020</t>
+  </si>
+  <si>
+    <t>0.9092,0.0770,0.0139,0.0035</t>
+  </si>
+  <si>
+    <t>0.9938,0.0025,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9911,0.0040,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9945,0.0017,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9946,0.0008,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.9842,0.0097,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9908,0.0051,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0014,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9965,0.0008,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9335,0.0804,0.0018,0.0021</t>
+  </si>
+  <si>
+    <t>0.5678,0.4494,0.0315,0.0004</t>
+  </si>
+  <si>
+    <t>0.8065,0.3377,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.0651,0.4540,0.8060,0.0011</t>
+  </si>
+  <si>
+    <t>0.8686,0.2244,0.0063,0.0006</t>
+  </si>
+  <si>
+    <t>0.9442,0.0594,0.0066,0.0028</t>
+  </si>
+  <si>
+    <t>0.9861,0.0127,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.6769,0.4432,0.0102,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.1895,0.9948,0.0003</t>
+  </si>
+  <si>
+    <t>0.9728,0.0236,0.0051,0.0008</t>
+  </si>
+  <si>
+    <t>0.0192,0.0047,0.9762,0.0026</t>
+  </si>
+  <si>
+    <t>0.0422,0.0672,0.9259,0.0051</t>
+  </si>
+  <si>
+    <t>0.0072,0.0008,0.9891,0.0031</t>
+  </si>
+  <si>
+    <t>0.0015,0.0746,0.9911,0.0008</t>
+  </si>
+  <si>
+    <t>0.0639,0.0054,0.9662,0.0002</t>
+  </si>
+  <si>
+    <t>0.0177,0.0012,0.9885,0.0003</t>
+  </si>
+  <si>
+    <t>0.0485,0.0063,0.9590,0.0014</t>
+  </si>
+  <si>
+    <t>0.5477,0.0579,0.5110,0.0099</t>
+  </si>
+  <si>
+    <t>0.1176,0.0025,0.9287,0.0022</t>
+  </si>
+  <si>
+    <t>0.1980,0.3834,0.4846,0.0073</t>
+  </si>
+  <si>
+    <t>0.6474,0.0414,0.4145,0.0054</t>
+  </si>
+  <si>
+    <t>0.2954,0.1529,0.5863,0.0053</t>
+  </si>
+  <si>
+    <t>0.5810,0.3462,0.0746,0.0047</t>
+  </si>
+  <si>
+    <t>0.6356,0.0788,0.2596,0.1468</t>
+  </si>
+  <si>
+    <t>0.5444,0.0505,0.5285,0.0090</t>
+  </si>
+  <si>
+    <t>0.5846,0.6308,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.7142,0.5136,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.8645,0.2591,0.0034,0.0008</t>
+  </si>
+  <si>
+    <t>0.9898,0.0119,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9350,0.1167,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.8318,0.0574,0.1125,0.0049</t>
+  </si>
+  <si>
+    <t>0.8728,0.0117,0.1353,0.0035</t>
+  </si>
+  <si>
+    <t>0.8316,0.0422,0.0744,0.0281</t>
+  </si>
+  <si>
+    <t>0.6388,0.0319,0.4437,0.0111</t>
+  </si>
+  <si>
+    <t>0.4642,0.0228,0.5522,0.0233</t>
+  </si>
+  <si>
+    <t>0.0072,0.0033,0.9738,0.0385</t>
+  </si>
+  <si>
+    <t>0.0223,0.6464,0.7911,0.0032</t>
+  </si>
+  <si>
+    <t>0.0628,0.1390,0.8744,0.0056</t>
+  </si>
+  <si>
+    <t>0.3637,0.0094,0.7904,0.0015</t>
+  </si>
+  <si>
+    <t>0.0173,0.8781,0.3462,0.0110</t>
+  </si>
+  <si>
+    <t>0.9955,0.0009,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9931,0.0081,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0013,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9896,0.0074,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9958,0.0025,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9963,0.0019,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0026,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0400,0.0102,0.9541,0.0070</t>
+  </si>
+  <si>
+    <t>0.2938,0.1795,0.6818,0.0047</t>
+  </si>
+  <si>
+    <t>0.9166,0.0416,0.0318,0.0087</t>
+  </si>
+  <si>
+    <t>0.0106,0.0135,0.9873,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.0019,0.9929,0.0020</t>
+  </si>
+  <si>
+    <t>0.0359,0.0702,0.9505,0.0009</t>
+  </si>
+  <si>
+    <t>0.0025,0.0074,0.9945,0.0007</t>
+  </si>
+  <si>
+    <t>0.0444,0.0182,0.9381,0.0011</t>
+  </si>
+  <si>
+    <t>0.0014,0.0058,0.9966,0.0004</t>
+  </si>
+  <si>
+    <t>0.0392,0.0173,0.9404,0.0060</t>
+  </si>
+  <si>
+    <t>0.0277,0.0730,0.9230,0.0034</t>
+  </si>
+  <si>
+    <t>0.6140,0.0434,0.3794,0.0246</t>
+  </si>
+  <si>
+    <t>0.4950,0.0298,0.5846,0.0097</t>
+  </si>
+  <si>
+    <t>0.7195,0.0526,0.1853,0.0517</t>
+  </si>
+  <si>
+    <t>0.9934,0.0040,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9923,0.0041,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9926,0.0078,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0007,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9861,0.0117,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9957,0.0025,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0253,0.3707,0.7655,0.0024</t>
+  </si>
+  <si>
+    <t>0.0058,0.2010,0.9624,0.0033</t>
+  </si>
+  <si>
+    <t>0.1310,0.0333,0.8525,0.0033</t>
+  </si>
+  <si>
+    <t>0.0492,0.0139,0.9411,0.0025</t>
+  </si>
+  <si>
+    <t>0.0386,0.0148,0.9413,0.0114</t>
+  </si>
+  <si>
+    <t>0.0612,0.0140,0.0452,0.9320</t>
+  </si>
+  <si>
+    <t>0.2074,0.0645,0.7374,0.1292</t>
+  </si>
+  <si>
+    <t>0.0448,0.0335,0.9133,0.0358</t>
+  </si>
+  <si>
+    <t>0.6071,0.0052,0.0045,0.5850</t>
+  </si>
+  <si>
+    <t>0.0635,0.0043,0.0002,0.9805</t>
+  </si>
+  <si>
+    <t>0.0297,0.0109,0.0013,0.9855</t>
+  </si>
+  <si>
+    <t>0.0061,0.0002,0.0001,0.9978</t>
+  </si>
+  <si>
+    <t>0.0062,0.0001,0.0000,0.9986</t>
+  </si>
+  <si>
+    <t>0.8462,0.0515,0.0243,0.0696</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1978,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2258,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2356,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2440,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2468,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,7 +2581,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2891,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3084,10 +3096,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,7 +3127,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,7 +3141,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3140,10 +3152,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>279</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3434,10 +3446,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3588,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3686,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3700,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3840,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3910,10 +3922,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3994,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,7 +4387,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,7 +4401,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4582,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4610,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D192" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,7 +4639,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4638,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4666,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4680,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D197" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4694,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D198" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4708,10 +4720,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D199" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4806,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4820,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4848,10 +4860,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4890,10 +4902,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5030,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5184,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5257,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5285,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5313,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5394,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5436,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
